--- a/AAII_Financials/Yearly/PURE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PURE_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/PURE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PURE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
   <si>
     <t>PURE</t>
   </si>
@@ -2841,7 +2841,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -2885,8 +2885,8 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>1000</v>
+      <c r="D62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>10</v>
